--- a/SuppXLS/Scen_z_MACC-RSD-CAP-WEM.xlsx
+++ b/SuppXLS/Scen_z_MACC-RSD-CAP-WEM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E55F94-BFCB-401A-965B-7E2CDCF8BEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87AB718-2B4E-488D-8849-D76B9F2012D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="217">
   <si>
     <t>Sum of Pv</t>
   </si>
@@ -688,10 +688,25 @@
     <t>District Heating (Commercial)</t>
   </si>
   <si>
-    <t>WAM</t>
-  </si>
-  <si>
     <t>UC_CAP</t>
+  </si>
+  <si>
+    <t>WAM NEP25</t>
+  </si>
+  <si>
+    <t>For projected years we have provided here the number of dwellings that undertake energy efficiency measures that bring the dwelling from a BER worse than B2 to one of B2 or better, excluding solar PV. This may not align exactly with the wording of the CAP target  of "B2 cost optimal or carbon equivalent". For 2024 we include an estimate of the cumulative number of dwellings that have undergone upgrade works  from 2018-2024 that improved their BER rating to B2 or better through SEAI schemes or Local Authority schemes, excluding solar PV only upgrades.</t>
+  </si>
+  <si>
+    <t>Assume that this item is for HP retrofits, excluding HP installed in new dwellings. The figure given for 2024 is the total number of HPs installed through SEAI and Local Authority retrofit schemes for 2019-2024.</t>
+  </si>
+  <si>
+    <t>Assume includes public services</t>
+  </si>
+  <si>
+    <t>FT-RSDHET</t>
+  </si>
+  <si>
+    <t>RSDHET</t>
   </si>
 </sst>
 </file>
@@ -701,13 +716,20 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1134,12 +1156,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1150,8 +1166,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1298,30 +1320,58 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1330,268 +1380,275 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="169">
+  <cellStyleXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="42" borderId="3" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="41"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="41"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="45"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="165"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="43" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="165" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="45"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="165"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="43" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="165" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="165" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" xfId="165" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="165" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="165" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="167"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="168"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="168" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="165" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="165" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="167"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="169"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="169" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="11" xfId="169" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="169" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="169" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="0" xfId="168" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="0" xfId="168" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="168" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="168" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="169" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="39" borderId="12" xfId="169" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="12" xfId="169" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="12" xfId="169" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="169" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="169" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="168" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="11" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="11" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="41" borderId="11" xfId="168" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="11" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="42" borderId="11" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="168" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="169" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="39" borderId="15" xfId="169" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="169" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="0" xfId="168" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="13" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="168" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="169" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="169" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="39" borderId="18" xfId="169" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="169" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="39" borderId="12" xfId="169" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="12" xfId="169" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="39" borderId="11" xfId="169" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="169" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="168" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="169" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="168" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="15" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="15" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="15" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="16" xfId="168" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="40" borderId="11" xfId="168" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="168" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="11" xfId="168" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="11" xfId="168" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="41" borderId="11" xfId="168" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="40" borderId="11" xfId="168" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="41" borderId="11" xfId="168" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="41" borderId="11" xfId="168" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="39" borderId="11" xfId="169" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="39" borderId="12" xfId="169" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="40" borderId="11" xfId="169" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="12" xfId="169" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="0" xfId="150" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="169">
+  <cellStyles count="174">
     <cellStyle name="20 % - Akzent1" xfId="72" hidden="1" xr:uid="{64AE4B0C-66F8-4587-9F6C-91708716F8BF}"/>
     <cellStyle name="20 % - Akzent1" xfId="97" hidden="1" xr:uid="{59AE85D3-364F-4FD3-B8B0-BF97C62F02A2}"/>
     <cellStyle name="20 % - Akzent1" xfId="138" hidden="1" xr:uid="{29BB96BD-8670-4A73-888B-A972E8A2ED68}"/>
@@ -1627,6 +1684,7 @@
     <cellStyle name="20% - Accent5" xfId="34" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - Accent5 2" xfId="65" xr:uid="{A18F35A9-0152-448E-A462-C268C0A78E01}"/>
     <cellStyle name="20% - Accent5 3" xfId="56" xr:uid="{2FF2EEBC-2788-4738-AC62-73DBD43DDC89}"/>
+    <cellStyle name="20% - Accent5 4" xfId="171" xr:uid="{1CAC032C-6C15-45A9-BBD9-E79857C360BC}"/>
     <cellStyle name="20% - Accent6" xfId="38" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - Accent6 2" xfId="58" xr:uid="{28B4310D-C2AB-43B0-B45A-353D0B8E7EAF}"/>
     <cellStyle name="40 % - Akzent1" xfId="73" hidden="1" xr:uid="{C170AF42-CD60-4B6D-BA77-3EB4551BAD43}"/>
@@ -1719,6 +1777,7 @@
     <cellStyle name="Comma 2 2 2" xfId="159" xr:uid="{8EFB9DC0-6C44-47F8-B231-05FC2337CF94}"/>
     <cellStyle name="Comma 2 3" xfId="158" xr:uid="{139D14AB-63A9-48F9-AC2E-0EEB4B9DE141}"/>
     <cellStyle name="Comma 3" xfId="157" xr:uid="{703859FE-28B4-412C-A532-7F29163E83CB}"/>
+    <cellStyle name="Comma 4" xfId="172" xr:uid="{F8C4EFE2-CE1F-441D-96B9-ADBD75A90FF5}"/>
     <cellStyle name="Ergebnis 8" xfId="71" hidden="1" xr:uid="{FF3AE49D-8094-4612-909D-1636D22B6171}"/>
     <cellStyle name="Ergebnis 8" xfId="144" hidden="1" xr:uid="{921B44CB-7ED9-4B7E-933B-39EDCCDB4517}"/>
     <cellStyle name="Erklärender Text 4" xfId="70" hidden="1" xr:uid="{E8E17030-30B1-49A2-B3C2-CCC13159460F}"/>
@@ -1742,12 +1801,14 @@
     <cellStyle name="Normal 3" xfId="63" xr:uid="{F51B5B94-E77C-4606-96FE-71E161D97B61}"/>
     <cellStyle name="Normal 3 2" xfId="66" xr:uid="{E8F04467-60F7-41C4-8DD1-3091C3C8EE15}"/>
     <cellStyle name="Normal 3 3" xfId="150" xr:uid="{DBAB067D-6568-44A4-8FF5-0B581401EE18}"/>
+    <cellStyle name="Normal 3 4" xfId="173" xr:uid="{B44AB211-DA7A-4B2B-B728-33F75B54AC65}"/>
     <cellStyle name="Normal 4" xfId="60" xr:uid="{13E4DEF3-1733-4208-84CC-4643C91F0373}"/>
     <cellStyle name="Normal 5" xfId="152" xr:uid="{1505F113-E93A-427E-9363-750539D86FF9}"/>
     <cellStyle name="Normal 5 2 2" xfId="153" xr:uid="{AF0D67E9-431D-4E01-9F56-C6AD63DC2FE5}"/>
     <cellStyle name="Normal 6" xfId="45" xr:uid="{9BDF725C-B4A7-4DD1-99E3-D6B1E843D8E2}"/>
     <cellStyle name="Normal 7" xfId="167" xr:uid="{4C270A53-0804-48F7-B3D2-5AC68A3D7D8B}"/>
     <cellStyle name="Normal 8" xfId="168" xr:uid="{28CCD77D-C619-4866-96E4-CE8CC73BB77A}"/>
+    <cellStyle name="Normal 9" xfId="169" xr:uid="{5A40138A-0D77-4109-9B0A-25D00084DD7D}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="43" xr:uid="{100800D8-EC1F-4C74-A177-951125BCCC6D}"/>
     <cellStyle name="Note 2" xfId="44" xr:uid="{400CBDC5-F4D7-4BD6-98FE-7098D08B57B3}"/>
     <cellStyle name="Note 2 2" xfId="166" xr:uid="{D35E2649-4474-4DE6-93B8-2397B6100CDC}"/>
@@ -1761,6 +1822,7 @@
     <cellStyle name="Warnender Text 4" xfId="69" hidden="1" xr:uid="{A5085B16-4C2E-4ACB-9174-0B94314B6C94}"/>
     <cellStyle name="Warnender Text 4" xfId="99" hidden="1" xr:uid="{C09DB00A-F599-4D0F-AE67-83064C5636DD}"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Worksheet Title" xfId="170" xr:uid="{894BD633-9C01-4332-A238-412594C72E19}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -4086,1116 +4148,1486 @@
       <c r="B25" s="8"/>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="D27" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="41" t="s">
+      <c r="C27" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="37"/>
+      <c r="E27" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="21">
         <v>2018</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="21">
         <v>2019</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="21">
         <v>2020</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="21">
         <v>2021</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27" s="21">
         <v>2022</v>
       </c>
-      <c r="K27" s="22">
+      <c r="K27" s="21">
         <v>2023</v>
       </c>
-      <c r="L27" s="22">
+      <c r="L27" s="21">
         <v>2024</v>
       </c>
-      <c r="M27" s="42">
+      <c r="M27" s="36">
         <v>2025</v>
       </c>
-      <c r="N27" s="22">
+      <c r="N27" s="21">
         <v>2026</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="21">
         <v>2027</v>
       </c>
-      <c r="P27" s="22">
+      <c r="P27" s="21">
         <v>2028</v>
       </c>
-      <c r="Q27" s="22">
+      <c r="Q27" s="21">
         <v>2029</v>
       </c>
-      <c r="R27" s="42">
+      <c r="R27" s="36">
         <v>2030</v>
       </c>
-      <c r="S27" s="22">
+      <c r="S27" s="21">
         <v>2031</v>
       </c>
-      <c r="T27" s="22">
+      <c r="T27" s="21">
         <v>2032</v>
       </c>
-      <c r="U27" s="22">
+      <c r="U27" s="21">
         <v>2033</v>
       </c>
-      <c r="V27" s="22">
+      <c r="V27" s="21">
         <v>2034</v>
       </c>
-      <c r="W27" s="22">
+      <c r="W27" s="21">
         <v>2035</v>
       </c>
-      <c r="X27" s="22">
+      <c r="X27" s="21">
         <v>2036</v>
       </c>
-      <c r="Y27" s="22">
+      <c r="Y27" s="21">
         <v>2037</v>
       </c>
-      <c r="Z27" s="22">
+      <c r="Z27" s="21">
         <v>2038</v>
       </c>
-      <c r="AA27" s="22">
+      <c r="AA27" s="21">
         <v>2039</v>
       </c>
-      <c r="AB27" s="42">
+      <c r="AB27" s="36">
         <v>2040</v>
       </c>
-      <c r="AC27" s="22">
+      <c r="AC27" s="21">
         <v>2041</v>
       </c>
-      <c r="AD27" s="22">
+      <c r="AD27" s="21">
         <v>2042</v>
       </c>
-      <c r="AE27" s="22">
+      <c r="AE27" s="21">
         <v>2043</v>
       </c>
-      <c r="AF27" s="22">
+      <c r="AF27" s="21">
         <v>2044</v>
       </c>
-      <c r="AG27" s="22">
+      <c r="AG27" s="21">
         <v>2045</v>
       </c>
-      <c r="AH27" s="22">
+      <c r="AH27" s="21">
         <v>2046</v>
       </c>
-      <c r="AI27" s="22">
+      <c r="AI27" s="21">
         <v>2047</v>
       </c>
-      <c r="AJ27" s="22">
+      <c r="AJ27" s="21">
         <v>2048</v>
       </c>
-      <c r="AK27" s="22">
+      <c r="AK27" s="21">
         <v>2049</v>
       </c>
-      <c r="AL27" s="42">
+      <c r="AL27" s="36">
         <v>2050</v>
       </c>
     </row>
     <row r="28" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="D28" s="24" t="s">
+      <c r="C28" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="D28" s="23"/>
+      <c r="E28" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="26">
-        <v>101505</v>
-      </c>
-      <c r="N28" s="27">
-        <v>147352</v>
-      </c>
-      <c r="O28" s="27">
-        <v>193199</v>
-      </c>
-      <c r="P28" s="27">
-        <v>239046</v>
-      </c>
-      <c r="Q28" s="27">
-        <v>284893</v>
-      </c>
-      <c r="R28" s="26">
-        <v>330740</v>
-      </c>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="25"/>
-      <c r="AC28" s="24"/>
-      <c r="AD28" s="24"/>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="24"/>
-      <c r="AH28" s="24"/>
-      <c r="AI28" s="24"/>
-      <c r="AJ28" s="24"/>
-      <c r="AK28" s="24"/>
-      <c r="AL28" s="25"/>
+      <c r="F28" s="38">
+        <v>4528</v>
+      </c>
+      <c r="G28" s="38">
+        <v>8473</v>
+      </c>
+      <c r="H28" s="38">
+        <v>12576</v>
+      </c>
+      <c r="I28" s="38">
+        <v>21085</v>
+      </c>
+      <c r="J28" s="38">
+        <v>36002</v>
+      </c>
+      <c r="K28" s="38">
+        <v>57730</v>
+      </c>
+      <c r="L28" s="38">
+        <v>76458.133004706353</v>
+      </c>
+      <c r="M28" s="38">
+        <v>101504.59834396423</v>
+      </c>
+      <c r="N28" s="38">
+        <v>131806.53391912146</v>
+      </c>
+      <c r="O28" s="38">
+        <v>168374.62820670515</v>
+      </c>
+      <c r="P28" s="38">
+        <v>212769.94018992549</v>
+      </c>
+      <c r="Q28" s="38">
+        <v>266253.76204901852</v>
+      </c>
+      <c r="R28" s="38">
+        <v>330739.76204901852</v>
+      </c>
+      <c r="S28" s="38">
+        <v>402894.63103844196</v>
+      </c>
+      <c r="T28" s="38">
+        <v>483270.38586238777</v>
+      </c>
+      <c r="U28" s="38">
+        <v>572769.39329977881</v>
+      </c>
+      <c r="V28" s="38">
+        <v>671364.76917221397</v>
+      </c>
+      <c r="W28" s="38">
+        <v>803011.76917221397</v>
+      </c>
+      <c r="X28" s="38">
+        <v>934123.03147115838</v>
+      </c>
+      <c r="Y28" s="38">
+        <v>1062667.5992603253</v>
+      </c>
+      <c r="Z28" s="38">
+        <v>1188757.2164680006</v>
+      </c>
+      <c r="AA28" s="38">
+        <v>1327958.622256465</v>
+      </c>
+      <c r="AB28" s="38">
+        <v>1470126.1569172072</v>
+      </c>
+      <c r="AC28" s="23"/>
+      <c r="AD28" s="23"/>
+      <c r="AE28" s="23"/>
+      <c r="AF28" s="23"/>
+      <c r="AG28" s="23"/>
+      <c r="AH28" s="23"/>
+      <c r="AI28" s="23"/>
+      <c r="AJ28" s="23"/>
+      <c r="AK28" s="23"/>
+      <c r="AL28" s="24"/>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="D29" s="24" t="s">
+      <c r="C29" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="D29" s="23"/>
+      <c r="E29" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="26">
-        <v>88430</v>
-      </c>
-      <c r="N29" s="28">
-        <v>126626</v>
-      </c>
-      <c r="O29" s="28">
-        <v>164822</v>
-      </c>
-      <c r="P29" s="28">
-        <v>203018</v>
-      </c>
-      <c r="Q29" s="28">
-        <v>241214</v>
-      </c>
-      <c r="R29" s="26">
-        <v>279410</v>
-      </c>
-      <c r="S29" s="24"/>
-      <c r="T29" s="24"/>
-      <c r="U29" s="24"/>
-      <c r="V29" s="24"/>
-      <c r="W29" s="24"/>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="25"/>
-      <c r="AC29" s="24"/>
-      <c r="AD29" s="24"/>
-      <c r="AE29" s="24"/>
-      <c r="AF29" s="24"/>
-      <c r="AG29" s="24"/>
-      <c r="AH29" s="24"/>
-      <c r="AI29" s="24"/>
-      <c r="AJ29" s="24"/>
-      <c r="AK29" s="24"/>
-      <c r="AL29" s="25"/>
+      <c r="F29" s="38">
+        <v>2791</v>
+      </c>
+      <c r="G29" s="38">
+        <v>6306</v>
+      </c>
+      <c r="H29" s="38">
+        <v>12228</v>
+      </c>
+      <c r="I29" s="38">
+        <v>23671</v>
+      </c>
+      <c r="J29" s="38">
+        <v>33157</v>
+      </c>
+      <c r="K29" s="38">
+        <v>46227</v>
+      </c>
+      <c r="L29" s="38">
+        <v>65580.100332647708</v>
+      </c>
+      <c r="M29" s="38">
+        <v>88429.861651536645</v>
+      </c>
+      <c r="N29" s="38">
+        <v>115259.45447616215</v>
+      </c>
+      <c r="O29" s="38">
+        <v>146809.32931771784</v>
+      </c>
+      <c r="P29" s="38">
+        <v>183964.44466028124</v>
+      </c>
+      <c r="Q29" s="38">
+        <v>227783.37094489671</v>
+      </c>
+      <c r="R29" s="38">
+        <v>279411.37094489671</v>
+      </c>
+      <c r="S29" s="38">
+        <v>332264.19836038561</v>
+      </c>
+      <c r="T29" s="38">
+        <v>387049.05666471604</v>
+      </c>
+      <c r="U29" s="38">
+        <v>443151.32676393108</v>
+      </c>
+      <c r="V29" s="38">
+        <v>501364.82754287875</v>
+      </c>
+      <c r="W29" s="38">
+        <v>533242.82754287869</v>
+      </c>
+      <c r="X29" s="38">
+        <v>553528.32832182629</v>
+      </c>
+      <c r="Y29" s="38">
+        <v>569779.54423927818</v>
+      </c>
+      <c r="Z29" s="38">
+        <v>578052.04909329861</v>
+      </c>
+      <c r="AA29" s="38">
+        <v>577462.83565678261</v>
+      </c>
+      <c r="AB29" s="38">
+        <v>570363.07433789363</v>
+      </c>
+      <c r="AC29" s="23"/>
+      <c r="AD29" s="23"/>
+      <c r="AE29" s="23"/>
+      <c r="AF29" s="23"/>
+      <c r="AG29" s="23"/>
+      <c r="AH29" s="23"/>
+      <c r="AI29" s="23"/>
+      <c r="AJ29" s="23"/>
+      <c r="AK29" s="23"/>
+      <c r="AL29" s="24"/>
     </row>
     <row r="30" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="D30" s="24" t="s">
+      <c r="C30" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="D30" s="19"/>
+      <c r="E30" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="29">
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="26">
         <v>61</v>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="26">
         <v>282</v>
       </c>
-      <c r="M30" s="28">
-        <v>459</v>
-      </c>
-      <c r="N30" s="28">
-        <v>636</v>
-      </c>
-      <c r="O30" s="28">
-        <v>813</v>
-      </c>
-      <c r="P30" s="28">
-        <v>990</v>
-      </c>
-      <c r="Q30" s="28">
-        <v>1167</v>
-      </c>
-      <c r="R30" s="47">
-        <v>1344</v>
-      </c>
-      <c r="S30" s="24"/>
-      <c r="T30" s="24"/>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="24"/>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="24"/>
-      <c r="AB30" s="25"/>
-      <c r="AC30" s="24"/>
-      <c r="AD30" s="24"/>
-      <c r="AE30" s="24"/>
-      <c r="AF30" s="24"/>
-      <c r="AG30" s="24"/>
-      <c r="AH30" s="24"/>
-      <c r="AI30" s="24"/>
-      <c r="AJ30" s="24"/>
-      <c r="AK30" s="24"/>
-      <c r="AL30" s="25"/>
+      <c r="M30" s="38">
+        <v>282</v>
+      </c>
+      <c r="N30" s="38">
+        <v>282</v>
+      </c>
+      <c r="O30" s="38">
+        <v>282</v>
+      </c>
+      <c r="P30" s="38">
+        <v>282</v>
+      </c>
+      <c r="Q30" s="38">
+        <v>282</v>
+      </c>
+      <c r="R30" s="38">
+        <v>282</v>
+      </c>
+      <c r="S30" s="38">
+        <v>282</v>
+      </c>
+      <c r="T30" s="38">
+        <v>282</v>
+      </c>
+      <c r="U30" s="38">
+        <v>282</v>
+      </c>
+      <c r="V30" s="38">
+        <v>282</v>
+      </c>
+      <c r="W30" s="38">
+        <v>282</v>
+      </c>
+      <c r="X30" s="38">
+        <v>282</v>
+      </c>
+      <c r="Y30" s="38">
+        <v>282</v>
+      </c>
+      <c r="Z30" s="38">
+        <v>282</v>
+      </c>
+      <c r="AA30" s="38">
+        <v>282</v>
+      </c>
+      <c r="AB30" s="38">
+        <v>282</v>
+      </c>
+      <c r="AC30" s="23"/>
+      <c r="AD30" s="23"/>
+      <c r="AE30" s="23"/>
+      <c r="AF30" s="23"/>
+      <c r="AG30" s="23"/>
+      <c r="AH30" s="23"/>
+      <c r="AI30" s="23"/>
+      <c r="AJ30" s="23"/>
+      <c r="AK30" s="23"/>
+      <c r="AL30" s="24"/>
     </row>
     <row r="31" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="D31" s="24" t="s">
+      <c r="C31" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="D31" s="19"/>
+      <c r="E31" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="26">
+      <c r="F31" s="38">
+        <v>10</v>
+      </c>
+      <c r="G31" s="38">
+        <v>57</v>
+      </c>
+      <c r="H31" s="38">
+        <v>103</v>
+      </c>
+      <c r="I31" s="38">
+        <v>208</v>
+      </c>
+      <c r="J31" s="38">
+        <v>379</v>
+      </c>
+      <c r="K31" s="38">
+        <v>675</v>
+      </c>
+      <c r="L31" s="38">
+        <v>937.5</v>
+      </c>
+      <c r="M31" s="38">
         <v>1200</v>
       </c>
-      <c r="N31" s="28">
+      <c r="N31" s="38">
         <v>2160</v>
       </c>
-      <c r="O31" s="28">
+      <c r="O31" s="38">
         <v>3120</v>
       </c>
-      <c r="P31" s="28">
+      <c r="P31" s="38">
         <v>4080</v>
       </c>
-      <c r="Q31" s="28">
+      <c r="Q31" s="38">
         <v>5040</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="38">
         <v>6000</v>
       </c>
-      <c r="S31" s="24"/>
-      <c r="T31" s="24"/>
-      <c r="U31" s="24"/>
-      <c r="V31" s="24"/>
-      <c r="W31" s="24"/>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
-      <c r="AA31" s="24"/>
-      <c r="AB31" s="25"/>
-      <c r="AC31" s="24"/>
-      <c r="AD31" s="24"/>
-      <c r="AE31" s="24"/>
-      <c r="AF31" s="24"/>
-      <c r="AG31" s="24"/>
-      <c r="AH31" s="24"/>
-      <c r="AI31" s="24"/>
-      <c r="AJ31" s="24"/>
-      <c r="AK31" s="24"/>
-      <c r="AL31" s="25"/>
+      <c r="S31" s="38">
+        <v>7800</v>
+      </c>
+      <c r="T31" s="38">
+        <v>9600</v>
+      </c>
+      <c r="U31" s="38">
+        <v>11400</v>
+      </c>
+      <c r="V31" s="38">
+        <v>13200</v>
+      </c>
+      <c r="W31" s="38">
+        <v>15000</v>
+      </c>
+      <c r="X31" s="38">
+        <v>14000</v>
+      </c>
+      <c r="Y31" s="38">
+        <v>13000</v>
+      </c>
+      <c r="Z31" s="38">
+        <v>12000</v>
+      </c>
+      <c r="AA31" s="38">
+        <v>11000</v>
+      </c>
+      <c r="AB31" s="38">
+        <v>10000</v>
+      </c>
+      <c r="AC31" s="23"/>
+      <c r="AD31" s="23"/>
+      <c r="AE31" s="23"/>
+      <c r="AF31" s="23"/>
+      <c r="AG31" s="23"/>
+      <c r="AH31" s="23"/>
+      <c r="AI31" s="23"/>
+      <c r="AJ31" s="23"/>
+      <c r="AK31" s="23"/>
+      <c r="AL31" s="24"/>
     </row>
     <row r="32" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="D32" s="24" t="s">
+      <c r="C32" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="D32" s="23"/>
+      <c r="E32" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="26">
-        <v>4810</v>
-      </c>
-      <c r="N32" s="28">
-        <v>8768</v>
-      </c>
-      <c r="O32" s="28">
-        <v>12726</v>
-      </c>
-      <c r="P32" s="28">
-        <v>16684</v>
-      </c>
-      <c r="Q32" s="28">
-        <v>20642</v>
-      </c>
-      <c r="R32" s="26">
+      <c r="F32" s="23">
+        <v>167</v>
+      </c>
+      <c r="G32" s="23">
+        <v>454</v>
+      </c>
+      <c r="H32" s="23">
+        <v>878</v>
+      </c>
+      <c r="I32" s="23">
+        <v>1770</v>
+      </c>
+      <c r="J32" s="23">
+        <v>2135</v>
+      </c>
+      <c r="K32" s="23">
+        <v>2856</v>
+      </c>
+      <c r="L32" s="23">
+        <v>3926.2142857142858</v>
+      </c>
+      <c r="M32" s="23">
+        <v>4996.4285714285716</v>
+      </c>
+      <c r="N32" s="23">
+        <v>8917.1428571428569</v>
+      </c>
+      <c r="O32" s="23">
+        <v>12837.857142857143</v>
+      </c>
+      <c r="P32" s="23">
+        <v>16758.571428571428</v>
+      </c>
+      <c r="Q32" s="23">
+        <v>20679.285714285714</v>
+      </c>
+      <c r="R32" s="23">
         <v>24600</v>
       </c>
-      <c r="S32" s="24"/>
-      <c r="T32" s="24"/>
-      <c r="U32" s="24"/>
-      <c r="V32" s="24"/>
-      <c r="W32" s="24"/>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
-      <c r="AA32" s="24"/>
-      <c r="AB32" s="25"/>
-      <c r="AC32" s="24"/>
-      <c r="AD32" s="24"/>
-      <c r="AE32" s="24"/>
-      <c r="AF32" s="24"/>
-      <c r="AG32" s="24"/>
-      <c r="AH32" s="24"/>
-      <c r="AI32" s="24"/>
-      <c r="AJ32" s="24"/>
-      <c r="AK32" s="24"/>
-      <c r="AL32" s="25"/>
+      <c r="S32" s="23">
+        <v>29090</v>
+      </c>
+      <c r="T32" s="23">
+        <v>33580</v>
+      </c>
+      <c r="U32" s="23">
+        <v>38070</v>
+      </c>
+      <c r="V32" s="23">
+        <v>42560</v>
+      </c>
+      <c r="W32" s="23">
+        <v>47050</v>
+      </c>
+      <c r="X32" s="23">
+        <v>69184.874566279919</v>
+      </c>
+      <c r="Y32" s="23">
+        <v>91319.749132559838</v>
+      </c>
+      <c r="Z32" s="23">
+        <v>113454.62369883976</v>
+      </c>
+      <c r="AA32" s="23">
+        <v>135589.49826511968</v>
+      </c>
+      <c r="AB32" s="23">
+        <v>157724.37283139961</v>
+      </c>
+      <c r="AC32" s="23"/>
+      <c r="AD32" s="23"/>
+      <c r="AE32" s="23"/>
+      <c r="AF32" s="23"/>
+      <c r="AG32" s="23"/>
+      <c r="AH32" s="23"/>
+      <c r="AI32" s="23"/>
+      <c r="AJ32" s="23"/>
+      <c r="AK32" s="23"/>
+      <c r="AL32" s="24"/>
     </row>
     <row r="33" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D33" s="30" t="s">
+      <c r="C33" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="D33" s="39"/>
+      <c r="E33" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="31">
+      <c r="F33" s="38">
+        <v>167</v>
+      </c>
+      <c r="G33" s="38">
+        <v>454</v>
+      </c>
+      <c r="H33" s="38">
+        <v>878</v>
+      </c>
+      <c r="I33" s="38">
+        <v>1770</v>
+      </c>
+      <c r="J33" s="38">
+        <v>2135</v>
+      </c>
+      <c r="K33" s="38">
+        <v>2821</v>
+      </c>
+      <c r="L33" s="38">
+        <v>3810.5</v>
+      </c>
+      <c r="M33" s="38">
         <v>4800</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="38">
         <v>8640</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="38">
         <v>12480</v>
       </c>
-      <c r="P33" s="20">
+      <c r="P33" s="38">
         <v>16320</v>
       </c>
-      <c r="Q33" s="20">
+      <c r="Q33" s="38">
         <v>20160</v>
       </c>
-      <c r="R33" s="31">
+      <c r="R33" s="38">
         <v>24000</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="18"/>
-      <c r="AD33" s="18"/>
-      <c r="AE33" s="18"/>
-      <c r="AF33" s="18"/>
-      <c r="AG33" s="18"/>
-      <c r="AH33" s="18"/>
-      <c r="AI33" s="18"/>
-      <c r="AJ33" s="18"/>
-      <c r="AK33" s="18"/>
-      <c r="AL33" s="32"/>
+      <c r="S33" s="38">
+        <v>28200</v>
+      </c>
+      <c r="T33" s="38">
+        <v>32400</v>
+      </c>
+      <c r="U33" s="38">
+        <v>36600</v>
+      </c>
+      <c r="V33" s="38">
+        <v>40800</v>
+      </c>
+      <c r="W33" s="38">
+        <v>45000</v>
+      </c>
+      <c r="X33" s="38">
+        <v>66844.874566279919</v>
+      </c>
+      <c r="Y33" s="38">
+        <v>88689.749132559838</v>
+      </c>
+      <c r="Z33" s="38">
+        <v>110534.62369883976</v>
+      </c>
+      <c r="AA33" s="38">
+        <v>132379.49826511968</v>
+      </c>
+      <c r="AB33" s="38">
+        <v>154224.37283139961</v>
+      </c>
+      <c r="AC33" s="29"/>
+      <c r="AD33" s="29"/>
+      <c r="AE33" s="29"/>
+      <c r="AF33" s="29"/>
+      <c r="AG33" s="29"/>
+      <c r="AH33" s="29"/>
+      <c r="AI33" s="29"/>
+      <c r="AJ33" s="29"/>
+      <c r="AK33" s="29"/>
+      <c r="AL33" s="30"/>
     </row>
     <row r="34" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D34" s="33" t="s">
+      <c r="C34" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="34" t="s">
+      <c r="D34" s="40"/>
+      <c r="E34" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="36">
+      <c r="F34" s="38">
+        <v>0</v>
+      </c>
+      <c r="G34" s="38">
+        <v>0</v>
+      </c>
+      <c r="H34" s="38">
+        <v>0</v>
+      </c>
+      <c r="I34" s="38">
+        <v>0</v>
+      </c>
+      <c r="J34" s="38">
+        <v>0</v>
+      </c>
+      <c r="K34" s="38">
+        <v>35</v>
+      </c>
+      <c r="L34" s="38">
+        <v>115.71428571428571</v>
+      </c>
+      <c r="M34" s="38">
+        <v>196.42857142857142</v>
+      </c>
+      <c r="N34" s="38">
+        <v>277.14285714285711</v>
+      </c>
+      <c r="O34" s="38">
+        <v>357.85714285714283</v>
+      </c>
+      <c r="P34" s="38">
+        <v>438.57142857142856</v>
+      </c>
+      <c r="Q34" s="38">
+        <v>519.28571428571422</v>
+      </c>
+      <c r="R34" s="38">
+        <v>600</v>
+      </c>
+      <c r="S34" s="38">
+        <v>890</v>
+      </c>
+      <c r="T34" s="38">
+        <v>1180</v>
+      </c>
+      <c r="U34" s="38">
+        <v>1470</v>
+      </c>
+      <c r="V34" s="38">
+        <v>1760</v>
+      </c>
+      <c r="W34" s="38">
+        <v>2050</v>
+      </c>
+      <c r="X34" s="38">
+        <v>2340</v>
+      </c>
+      <c r="Y34" s="38">
+        <v>2630</v>
+      </c>
+      <c r="Z34" s="38">
+        <v>2920</v>
+      </c>
+      <c r="AA34" s="38">
+        <v>3210</v>
+      </c>
+      <c r="AB34" s="38">
+        <v>3500</v>
+      </c>
+      <c r="AC34" s="33"/>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
+      <c r="AI34" s="33"/>
+      <c r="AJ34" s="33"/>
+      <c r="AK34" s="33"/>
+      <c r="AL34" s="34"/>
+    </row>
+    <row r="35" spans="2:40" x14ac:dyDescent="0.25">
+      <c r="C35" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D35" s="23"/>
+      <c r="E35" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="38">
+        <v>4740.55</v>
+      </c>
+      <c r="M35" s="38">
+        <v>5044.28125</v>
+      </c>
+      <c r="N35" s="38">
+        <v>5540.25</v>
+      </c>
+      <c r="O35" s="38">
+        <v>5865.5</v>
+      </c>
+      <c r="P35" s="38">
+        <v>6207.875</v>
+      </c>
+      <c r="Q35" s="38">
+        <v>6579.75</v>
+      </c>
+      <c r="R35" s="38">
+        <v>6930.625</v>
+      </c>
+      <c r="S35" s="38">
+        <v>7281.125</v>
+      </c>
+      <c r="T35" s="38">
+        <v>7685.25</v>
+      </c>
+      <c r="U35" s="38">
+        <v>8093.125</v>
+      </c>
+      <c r="V35" s="38">
+        <v>8507.5</v>
+      </c>
+      <c r="W35" s="38">
+        <v>8927.125</v>
+      </c>
+      <c r="X35" s="38">
+        <v>9282</v>
+      </c>
+      <c r="Y35" s="38">
+        <v>9591.5</v>
+      </c>
+      <c r="Z35" s="38">
+        <v>9953.25</v>
+      </c>
+      <c r="AA35" s="38">
+        <v>10242.5</v>
+      </c>
+      <c r="AB35" s="38">
+        <v>10550.5</v>
+      </c>
+      <c r="AC35" s="23"/>
+      <c r="AD35" s="23"/>
+      <c r="AE35" s="23"/>
+      <c r="AF35" s="23"/>
+      <c r="AG35" s="23"/>
+      <c r="AH35" s="23"/>
+      <c r="AI35" s="23"/>
+      <c r="AJ35" s="23"/>
+      <c r="AK35" s="23"/>
+      <c r="AL35" s="24"/>
+    </row>
+    <row r="36" spans="2:40" x14ac:dyDescent="0.25">
+      <c r="C36" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="38">
+        <v>25</v>
+      </c>
+      <c r="M36" s="38">
+        <v>25</v>
+      </c>
+      <c r="N36" s="38">
+        <v>25</v>
+      </c>
+      <c r="O36" s="38">
+        <v>25</v>
+      </c>
+      <c r="P36" s="38">
+        <v>25</v>
+      </c>
+      <c r="Q36" s="38">
+        <v>231.25</v>
+      </c>
+      <c r="R36" s="38">
+        <v>1525</v>
+      </c>
+      <c r="S36" s="38">
+        <v>2862.5</v>
+      </c>
+      <c r="T36" s="38">
+        <v>3500</v>
+      </c>
+      <c r="U36" s="38">
+        <v>4000</v>
+      </c>
+      <c r="V36" s="38">
+        <v>4500</v>
+      </c>
+      <c r="W36" s="38">
+        <v>5175</v>
+      </c>
+      <c r="X36" s="38">
+        <v>5875</v>
+      </c>
+      <c r="Y36" s="38">
+        <v>6575</v>
+      </c>
+      <c r="Z36" s="38">
+        <v>7350</v>
+      </c>
+      <c r="AA36" s="38">
+        <v>8350</v>
+      </c>
+      <c r="AB36" s="38">
+        <v>9325</v>
+      </c>
+      <c r="AC36" s="23"/>
+      <c r="AD36" s="23"/>
+      <c r="AE36" s="23"/>
+      <c r="AF36" s="23"/>
+      <c r="AG36" s="23"/>
+      <c r="AH36" s="23"/>
+      <c r="AI36" s="23"/>
+      <c r="AJ36" s="23"/>
+      <c r="AK36" s="23"/>
+      <c r="AL36" s="24"/>
+    </row>
+    <row r="37" spans="2:40" x14ac:dyDescent="0.25">
+      <c r="C37" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="38">
+        <v>914.93749999999989</v>
+      </c>
+      <c r="M37" s="38">
+        <v>1680.75</v>
+      </c>
+      <c r="N37" s="38">
+        <v>2789.75</v>
+      </c>
+      <c r="O37" s="38">
+        <v>3543.375</v>
+      </c>
+      <c r="P37" s="38">
+        <v>4296.75</v>
+      </c>
+      <c r="Q37" s="38">
+        <v>5050.375</v>
+      </c>
+      <c r="R37" s="38">
+        <v>5805.25</v>
+      </c>
+      <c r="S37" s="38">
+        <v>6505.5</v>
+      </c>
+      <c r="T37" s="38">
+        <v>7105.375</v>
+      </c>
+      <c r="U37" s="38">
+        <v>7695.375</v>
+      </c>
+      <c r="V37" s="38">
+        <v>8277.75</v>
+      </c>
+      <c r="W37" s="38">
+        <v>8857.625</v>
+      </c>
+      <c r="X37" s="38">
+        <v>9402.375</v>
+      </c>
+      <c r="Y37" s="38">
+        <v>9880</v>
+      </c>
+      <c r="Z37" s="38">
+        <v>10349.75</v>
+      </c>
+      <c r="AA37" s="38">
+        <v>10812.75</v>
+      </c>
+      <c r="AB37" s="38">
+        <v>11268.5</v>
+      </c>
+      <c r="AC37" s="23"/>
+      <c r="AD37" s="23"/>
+      <c r="AE37" s="23"/>
+      <c r="AF37" s="23"/>
+      <c r="AG37" s="23"/>
+      <c r="AH37" s="23"/>
+      <c r="AI37" s="23"/>
+      <c r="AJ37" s="23"/>
+      <c r="AK37" s="23"/>
+      <c r="AL37" s="24"/>
+    </row>
+    <row r="38" spans="2:40" x14ac:dyDescent="0.25">
+      <c r="C38" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="E38" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="38">
         <v>10</v>
       </c>
-      <c r="N34" s="37">
-        <v>128</v>
-      </c>
-      <c r="O34" s="37">
-        <v>246</v>
-      </c>
-      <c r="P34" s="37">
-        <v>364</v>
-      </c>
-      <c r="Q34" s="37">
-        <v>482</v>
-      </c>
-      <c r="R34" s="36">
-        <v>600</v>
-      </c>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35"/>
-      <c r="W34" s="35"/>
-      <c r="X34" s="35"/>
-      <c r="Y34" s="35"/>
-      <c r="Z34" s="35"/>
-      <c r="AA34" s="35"/>
-      <c r="AB34" s="38"/>
-      <c r="AC34" s="35"/>
-      <c r="AD34" s="35"/>
-      <c r="AE34" s="35"/>
-      <c r="AF34" s="35"/>
-      <c r="AG34" s="35"/>
-      <c r="AH34" s="35"/>
-      <c r="AI34" s="35"/>
-      <c r="AJ34" s="35"/>
-      <c r="AK34" s="35"/>
-      <c r="AL34" s="39"/>
-    </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D35" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="25">
-        <v>5318</v>
-      </c>
-      <c r="M35" s="25">
-        <v>5824</v>
-      </c>
-      <c r="N35" s="25">
-        <v>6065</v>
-      </c>
-      <c r="O35" s="25">
-        <v>6565</v>
-      </c>
-      <c r="P35" s="25">
-        <v>6805</v>
-      </c>
-      <c r="Q35" s="25">
-        <v>7105</v>
-      </c>
-      <c r="R35" s="25">
-        <v>7155</v>
-      </c>
-      <c r="S35" s="25">
-        <v>7355</v>
-      </c>
-      <c r="T35" s="25">
-        <v>7555</v>
-      </c>
-      <c r="U35" s="25">
-        <v>7755</v>
-      </c>
-      <c r="V35" s="25">
-        <v>7955</v>
-      </c>
-      <c r="W35" s="25">
-        <v>8155</v>
-      </c>
-      <c r="X35" s="25">
-        <v>8355</v>
-      </c>
-      <c r="Y35" s="25">
-        <v>8555</v>
-      </c>
-      <c r="Z35" s="25">
-        <v>8755</v>
-      </c>
-      <c r="AA35" s="25">
-        <v>8955</v>
-      </c>
-      <c r="AB35" s="25">
-        <v>9155</v>
-      </c>
-      <c r="AC35" s="24"/>
-      <c r="AD35" s="24"/>
-      <c r="AE35" s="24"/>
-      <c r="AF35" s="24"/>
-      <c r="AG35" s="24"/>
-      <c r="AH35" s="24"/>
-      <c r="AI35" s="24"/>
-      <c r="AJ35" s="24"/>
-      <c r="AK35" s="24"/>
-      <c r="AL35" s="25"/>
-    </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D36" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="25">
-        <v>25</v>
-      </c>
-      <c r="M36" s="25">
-        <v>25</v>
-      </c>
-      <c r="N36" s="25">
-        <v>25</v>
-      </c>
-      <c r="O36" s="25">
-        <v>25</v>
-      </c>
-      <c r="P36" s="25">
-        <v>850</v>
-      </c>
-      <c r="Q36" s="25">
-        <v>2650</v>
-      </c>
-      <c r="R36" s="25">
-        <v>4000</v>
-      </c>
-      <c r="S36" s="25">
-        <v>5000</v>
-      </c>
-      <c r="T36" s="25">
-        <v>5700</v>
-      </c>
-      <c r="U36" s="25">
-        <v>6500</v>
-      </c>
-      <c r="V36" s="25">
-        <v>7100</v>
-      </c>
-      <c r="W36" s="25">
-        <v>7800</v>
-      </c>
-      <c r="X36" s="25">
-        <v>8500</v>
-      </c>
-      <c r="Y36" s="25">
-        <v>9200</v>
-      </c>
-      <c r="Z36" s="25">
-        <v>9900</v>
-      </c>
-      <c r="AA36" s="25">
-        <v>10600</v>
-      </c>
-      <c r="AB36" s="25">
-        <v>11300</v>
-      </c>
-      <c r="AC36" s="24"/>
-      <c r="AD36" s="24"/>
-      <c r="AE36" s="24"/>
-      <c r="AF36" s="24"/>
-      <c r="AG36" s="24"/>
-      <c r="AH36" s="24"/>
-      <c r="AI36" s="24"/>
-      <c r="AJ36" s="24"/>
-      <c r="AK36" s="24"/>
-      <c r="AL36" s="25"/>
-    </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D37" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="25">
-        <v>1194</v>
-      </c>
-      <c r="M37" s="25">
-        <v>2249</v>
-      </c>
-      <c r="N37" s="25">
-        <v>2687</v>
-      </c>
-      <c r="O37" s="25">
-        <v>3575</v>
-      </c>
-      <c r="P37" s="25">
-        <v>4192</v>
-      </c>
-      <c r="Q37" s="25">
-        <v>5324</v>
-      </c>
-      <c r="R37" s="25">
-        <v>6500</v>
-      </c>
-      <c r="S37" s="25">
-        <v>6750</v>
-      </c>
-      <c r="T37" s="25">
-        <v>7050</v>
-      </c>
-      <c r="U37" s="25">
-        <v>7350</v>
-      </c>
-      <c r="V37" s="25">
-        <v>7650</v>
-      </c>
-      <c r="W37" s="25">
-        <v>7950</v>
-      </c>
-      <c r="X37" s="25">
-        <v>8250</v>
-      </c>
-      <c r="Y37" s="25">
-        <v>8550</v>
-      </c>
-      <c r="Z37" s="25">
-        <v>8850</v>
-      </c>
-      <c r="AA37" s="25">
-        <v>9150</v>
-      </c>
-      <c r="AB37" s="25">
-        <v>9450</v>
-      </c>
-      <c r="AC37" s="24"/>
-      <c r="AD37" s="24"/>
-      <c r="AE37" s="24"/>
-      <c r="AF37" s="24"/>
-      <c r="AG37" s="24"/>
-      <c r="AH37" s="24"/>
-      <c r="AI37" s="24"/>
-      <c r="AJ37" s="24"/>
-      <c r="AK37" s="24"/>
-      <c r="AL37" s="25"/>
-    </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D38" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="E38" s="23" t="s">
+      <c r="N38" s="25">
+        <v>10</v>
+      </c>
+      <c r="O38" s="25">
+        <v>10</v>
+      </c>
+      <c r="P38" s="25">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="25">
+        <v>10</v>
+      </c>
+      <c r="R38" s="38">
+        <v>10</v>
+      </c>
+      <c r="S38" s="20">
+        <v>10</v>
+      </c>
+      <c r="T38" s="20">
+        <v>10</v>
+      </c>
+      <c r="U38" s="20">
+        <v>10</v>
+      </c>
+      <c r="V38" s="20">
+        <v>10</v>
+      </c>
+      <c r="W38" s="20">
+        <v>10</v>
+      </c>
+      <c r="X38" s="20">
+        <v>10</v>
+      </c>
+      <c r="Y38" s="20">
+        <v>10</v>
+      </c>
+      <c r="Z38" s="20">
+        <v>10</v>
+      </c>
+      <c r="AA38" s="20">
+        <v>10</v>
+      </c>
+      <c r="AB38" s="20">
+        <v>10</v>
+      </c>
+      <c r="AC38" s="23"/>
+      <c r="AD38" s="23"/>
+      <c r="AE38" s="23"/>
+      <c r="AF38" s="23"/>
+      <c r="AG38" s="23"/>
+      <c r="AH38" s="23"/>
+      <c r="AI38" s="23"/>
+      <c r="AJ38" s="23"/>
+      <c r="AK38" s="23"/>
+      <c r="AL38" s="24"/>
+    </row>
+    <row r="39" spans="2:40" x14ac:dyDescent="0.25">
+      <c r="C39" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="23"/>
+      <c r="E39" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="26">
-        <v>10</v>
-      </c>
-      <c r="N38" s="28">
-        <v>10</v>
-      </c>
-      <c r="O38" s="28">
-        <v>10</v>
-      </c>
-      <c r="P38" s="28">
-        <v>10</v>
-      </c>
-      <c r="Q38" s="28">
-        <v>10</v>
-      </c>
-      <c r="R38" s="26">
-        <v>10</v>
-      </c>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
-      <c r="U38" s="24"/>
-      <c r="V38" s="24"/>
-      <c r="W38" s="24"/>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="25"/>
-      <c r="AC38" s="24"/>
-      <c r="AD38" s="24"/>
-      <c r="AE38" s="24"/>
-      <c r="AF38" s="24"/>
-      <c r="AG38" s="24"/>
-      <c r="AH38" s="24"/>
-      <c r="AI38" s="24"/>
-      <c r="AJ38" s="24"/>
-      <c r="AK38" s="24"/>
-      <c r="AL38" s="25"/>
-    </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D39" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="26">
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="38">
         <v>12</v>
       </c>
-      <c r="N39" s="28">
+      <c r="N39" s="25">
         <v>13.6</v>
       </c>
-      <c r="O39" s="28">
+      <c r="O39" s="25">
         <v>15.2</v>
       </c>
-      <c r="P39" s="28">
+      <c r="P39" s="25">
         <v>16.8</v>
       </c>
-      <c r="Q39" s="28">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="R39" s="26">
+      <c r="Q39" s="25">
+        <v>18.400000000000002</v>
+      </c>
+      <c r="R39" s="38">
         <v>20</v>
       </c>
-      <c r="S39" s="24"/>
-      <c r="T39" s="24"/>
-      <c r="U39" s="24"/>
-      <c r="V39" s="24"/>
-      <c r="W39" s="24"/>
-      <c r="X39" s="24"/>
-      <c r="Y39" s="24"/>
-      <c r="Z39" s="24"/>
-      <c r="AA39" s="24"/>
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="24"/>
-      <c r="AD39" s="24"/>
-      <c r="AE39" s="24"/>
-      <c r="AF39" s="24"/>
-      <c r="AG39" s="24"/>
-      <c r="AH39" s="24"/>
-      <c r="AI39" s="24"/>
-      <c r="AJ39" s="24"/>
-      <c r="AK39" s="24"/>
-      <c r="AL39" s="25"/>
+      <c r="S39" s="20">
+        <v>20</v>
+      </c>
+      <c r="T39" s="20">
+        <v>20</v>
+      </c>
+      <c r="U39" s="20">
+        <v>20</v>
+      </c>
+      <c r="V39" s="20">
+        <v>20</v>
+      </c>
+      <c r="W39" s="20">
+        <v>20</v>
+      </c>
+      <c r="X39" s="20">
+        <v>20</v>
+      </c>
+      <c r="Y39" s="20">
+        <v>20</v>
+      </c>
+      <c r="Z39" s="20">
+        <v>20</v>
+      </c>
+      <c r="AA39" s="20">
+        <v>20</v>
+      </c>
+      <c r="AB39" s="20">
+        <v>20</v>
+      </c>
+      <c r="AC39" s="23"/>
+      <c r="AD39" s="23"/>
+      <c r="AE39" s="23"/>
+      <c r="AF39" s="23"/>
+      <c r="AG39" s="23"/>
+      <c r="AH39" s="23"/>
+      <c r="AI39" s="23"/>
+      <c r="AJ39" s="23"/>
+      <c r="AK39" s="23"/>
+      <c r="AL39" s="24"/>
     </row>
     <row r="40" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D40" s="24" t="s">
+      <c r="C40" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="D40" s="23"/>
+      <c r="E40" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="26">
-        <v>0</v>
-      </c>
-      <c r="N40" s="44">
-        <v>0.86</v>
-      </c>
-      <c r="O40" s="44">
-        <v>1.72</v>
-      </c>
-      <c r="P40" s="44">
-        <v>2.58</v>
-      </c>
-      <c r="Q40" s="44">
-        <v>3.44</v>
-      </c>
-      <c r="R40" s="45">
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="42">
+        <v>0.25</v>
+      </c>
+      <c r="N40" s="42">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="O40" s="42">
+        <v>0.8</v>
+      </c>
+      <c r="P40" s="42">
+        <v>1.45</v>
+      </c>
+      <c r="Q40" s="42">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="R40" s="42">
         <v>4.3</v>
       </c>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="24"/>
-      <c r="Z40" s="24"/>
-      <c r="AA40" s="24"/>
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="24"/>
-      <c r="AD40" s="24"/>
-      <c r="AE40" s="24"/>
-      <c r="AF40" s="24"/>
-      <c r="AG40" s="24"/>
-      <c r="AH40" s="24"/>
-      <c r="AI40" s="24"/>
-      <c r="AJ40" s="24"/>
-      <c r="AK40" s="24"/>
-      <c r="AL40" s="25"/>
+      <c r="S40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="T40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="U40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="V40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="W40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="X40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="Y40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="Z40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="AA40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="AB40" s="42">
+        <v>5.7</v>
+      </c>
+      <c r="AC40" s="23"/>
+      <c r="AD40" s="23"/>
+      <c r="AE40" s="23"/>
+      <c r="AF40" s="23"/>
+      <c r="AG40" s="23"/>
+      <c r="AH40" s="23"/>
+      <c r="AI40" s="23"/>
+      <c r="AJ40" s="23"/>
+      <c r="AK40" s="23"/>
+      <c r="AL40" s="24"/>
     </row>
     <row r="41" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D41" s="24" t="s">
+      <c r="C41" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="D41" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="F41" s="25">
-        <v>2566</v>
-      </c>
-      <c r="G41" s="25">
-        <v>4989</v>
-      </c>
-      <c r="H41" s="25">
-        <v>8264</v>
-      </c>
-      <c r="I41" s="25">
-        <v>12603</v>
-      </c>
-      <c r="J41" s="25">
-        <v>21079</v>
-      </c>
-      <c r="K41" s="25">
-        <v>38679</v>
-      </c>
-      <c r="L41" s="25">
-        <v>60496</v>
-      </c>
-      <c r="M41" s="25">
-        <v>86728</v>
-      </c>
-      <c r="N41" s="28">
-        <v>114601</v>
-      </c>
-      <c r="O41" s="28">
-        <v>146309</v>
-      </c>
-      <c r="P41" s="28">
-        <v>181849</v>
-      </c>
-      <c r="Q41" s="28">
-        <v>221224</v>
-      </c>
-      <c r="R41" s="28">
-        <v>264432</v>
-      </c>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
-      <c r="AA41" s="24"/>
-      <c r="AB41" s="25"/>
-      <c r="AC41" s="24"/>
-      <c r="AD41" s="24"/>
-      <c r="AE41" s="24"/>
-      <c r="AF41" s="24"/>
-      <c r="AG41" s="24"/>
-      <c r="AH41" s="24"/>
-      <c r="AI41" s="24"/>
-      <c r="AJ41" s="24"/>
-      <c r="AK41" s="24"/>
-      <c r="AL41" s="25"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="44">
+        <v>30290</v>
+      </c>
+      <c r="M41" s="38">
+        <v>10808</v>
+      </c>
+      <c r="N41" s="43">
+        <v>25024.6</v>
+      </c>
+      <c r="O41" s="43">
+        <v>39241.199999999997</v>
+      </c>
+      <c r="P41" s="43">
+        <v>53457.799999999996</v>
+      </c>
+      <c r="Q41" s="43">
+        <v>67674.399999999994</v>
+      </c>
+      <c r="R41" s="38">
+        <v>81891</v>
+      </c>
+      <c r="S41" s="43">
+        <v>100657.8</v>
+      </c>
+      <c r="T41" s="43">
+        <v>119424.6</v>
+      </c>
+      <c r="U41" s="43">
+        <v>138191.4</v>
+      </c>
+      <c r="V41" s="43">
+        <v>156958.19999999998</v>
+      </c>
+      <c r="W41" s="43">
+        <v>175724.99999999997</v>
+      </c>
+      <c r="X41" s="43">
+        <v>194491.79999999996</v>
+      </c>
+      <c r="Y41" s="43">
+        <v>213258.59999999995</v>
+      </c>
+      <c r="Z41" s="43">
+        <v>232025.39999999994</v>
+      </c>
+      <c r="AA41" s="43">
+        <v>250792.19999999992</v>
+      </c>
+      <c r="AB41" s="38">
+        <v>269559</v>
+      </c>
+      <c r="AC41" s="23"/>
+      <c r="AD41" s="23"/>
+      <c r="AE41" s="23"/>
+      <c r="AF41" s="23"/>
+      <c r="AG41" s="23"/>
+      <c r="AH41" s="23"/>
+      <c r="AI41" s="23"/>
+      <c r="AJ41" s="23"/>
+      <c r="AK41" s="23"/>
+      <c r="AL41" s="24"/>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="C42" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="D42" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="E42" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="F42" s="25">
-        <v>229</v>
-      </c>
-      <c r="G42" s="25">
-        <v>1358</v>
-      </c>
-      <c r="H42" s="25">
-        <v>2813</v>
-      </c>
-      <c r="I42" s="25">
-        <v>4784</v>
-      </c>
-      <c r="J42" s="25">
-        <v>7056</v>
-      </c>
-      <c r="K42" s="25">
-        <v>10823</v>
-      </c>
-      <c r="L42" s="25">
-        <v>14423</v>
-      </c>
-      <c r="M42" s="25">
-        <v>18770</v>
-      </c>
-      <c r="N42" s="28">
-        <v>43616</v>
-      </c>
-      <c r="O42" s="28">
-        <v>68462</v>
-      </c>
-      <c r="P42" s="28">
-        <v>93308</v>
-      </c>
-      <c r="Q42" s="28">
-        <v>118154</v>
-      </c>
-      <c r="R42" s="28">
-        <v>143000</v>
-      </c>
-      <c r="S42" s="24"/>
-      <c r="T42" s="24"/>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
-      <c r="W42" s="24"/>
-      <c r="X42" s="24"/>
-      <c r="Y42" s="24"/>
-      <c r="Z42" s="24"/>
-      <c r="AA42" s="24"/>
-      <c r="AB42" s="25"/>
-      <c r="AC42" s="24"/>
-      <c r="AD42" s="24"/>
-      <c r="AE42" s="24"/>
-      <c r="AF42" s="24"/>
-      <c r="AG42" s="24"/>
-      <c r="AH42" s="24"/>
-      <c r="AI42" s="24"/>
-      <c r="AJ42" s="24"/>
-      <c r="AK42" s="24"/>
-      <c r="AL42" s="25"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="38">
+        <v>22594</v>
+      </c>
+      <c r="M42" s="38">
+        <v>31445.340470809999</v>
+      </c>
+      <c r="N42" s="38">
+        <v>53015.009948920997</v>
+      </c>
+      <c r="O42" s="38">
+        <v>74768.033133266013</v>
+      </c>
+      <c r="P42" s="38">
+        <v>97085.80137452601</v>
+      </c>
+      <c r="Q42" s="38">
+        <v>119719.602917269</v>
+      </c>
+      <c r="R42" s="38">
+        <v>142350.36580480903</v>
+      </c>
+      <c r="S42" s="38">
+        <v>165081.94181390601</v>
+      </c>
+      <c r="T42" s="38">
+        <v>187346.88963736803</v>
+      </c>
+      <c r="U42" s="38">
+        <v>210029.48462770402</v>
+      </c>
+      <c r="V42" s="38">
+        <v>232675.82927241101</v>
+      </c>
+      <c r="W42" s="38">
+        <v>254838.99066632299</v>
+      </c>
+      <c r="X42" s="38">
+        <v>277005.17211469699</v>
+      </c>
+      <c r="Y42" s="38">
+        <v>299162.26804125699</v>
+      </c>
+      <c r="Z42" s="38">
+        <v>321719.28957132105</v>
+      </c>
+      <c r="AA42" s="38">
+        <v>338758.85337760701</v>
+      </c>
+      <c r="AB42" s="38">
+        <v>407140.970632207</v>
+      </c>
+      <c r="AC42" s="23"/>
+      <c r="AD42" s="23"/>
+      <c r="AE42" s="23"/>
+      <c r="AF42" s="23"/>
+      <c r="AG42" s="23"/>
+      <c r="AH42" s="23"/>
+      <c r="AI42" s="23"/>
+      <c r="AJ42" s="23"/>
+      <c r="AK42" s="23"/>
+      <c r="AL42" s="24"/>
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D43" s="24" t="s">
+      <c r="C43" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="D43" s="23"/>
+      <c r="E43" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="26">
-        <v>0</v>
-      </c>
-      <c r="N43" s="44">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="O43" s="44">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="P43" s="44">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="Q43" s="44">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="R43" s="45">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
-      <c r="U43" s="24"/>
-      <c r="V43" s="24"/>
-      <c r="W43" s="24"/>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24"/>
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="24"/>
-      <c r="AD43" s="24"/>
-      <c r="AE43" s="24"/>
-      <c r="AF43" s="24"/>
-      <c r="AG43" s="24"/>
-      <c r="AH43" s="24"/>
-      <c r="AI43" s="24"/>
-      <c r="AJ43" s="24"/>
-      <c r="AK43" s="24"/>
-      <c r="AL43" s="25"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="41">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="K43" s="41">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="L43" s="41">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="M43" s="41">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="N43" s="41">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="O43" s="41">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="P43" s="41">
+        <v>1.5754000000000001E-2</v>
+      </c>
+      <c r="Q43" s="41">
+        <v>3.0107999999999999E-2</v>
+      </c>
+      <c r="R43" s="41">
+        <v>4.4462000000000002E-2</v>
+      </c>
+      <c r="S43" s="41">
+        <v>9.401580000000001E-2</v>
+      </c>
+      <c r="T43" s="41">
+        <v>0.14356960000000002</v>
+      </c>
+      <c r="U43" s="41">
+        <v>0.1931234</v>
+      </c>
+      <c r="V43" s="41">
+        <v>0.24267720000000001</v>
+      </c>
+      <c r="W43" s="41">
+        <v>0.29223100000000002</v>
+      </c>
+      <c r="X43" s="41">
+        <v>0.3417848</v>
+      </c>
+      <c r="Y43" s="41">
+        <v>0.39133860000000004</v>
+      </c>
+      <c r="Z43" s="41">
+        <v>0.44089240000000002</v>
+      </c>
+      <c r="AA43" s="41">
+        <v>0.4904462</v>
+      </c>
+      <c r="AB43" s="41">
+        <v>0.54</v>
+      </c>
+      <c r="AC43" s="23"/>
+      <c r="AD43" s="23"/>
+      <c r="AE43" s="23"/>
+      <c r="AF43" s="23"/>
+      <c r="AG43" s="23"/>
+      <c r="AH43" s="23"/>
+      <c r="AI43" s="23"/>
+      <c r="AJ43" s="23"/>
+      <c r="AK43" s="23"/>
+      <c r="AL43" s="24"/>
     </row>
     <row r="44" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D44" s="24" t="s">
+      <c r="C44" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="D44" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="40">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="K44" s="46">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="L44" s="46">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="M44" s="46">
-        <v>8.6E-3</v>
-      </c>
-      <c r="N44" s="46">
-        <v>0.01</v>
-      </c>
-      <c r="O44" s="46">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="P44" s="46">
-        <v>0.08</v>
-      </c>
-      <c r="Q44" s="46">
-        <v>0.115</v>
-      </c>
-      <c r="R44" s="46">
-        <v>0.15</v>
-      </c>
-      <c r="S44" s="24"/>
-      <c r="T44" s="24"/>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
-      <c r="W44" s="24"/>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="24"/>
-      <c r="AD44" s="24"/>
-      <c r="AE44" s="24"/>
-      <c r="AF44" s="24"/>
-      <c r="AG44" s="24"/>
-      <c r="AH44" s="24"/>
-      <c r="AI44" s="24"/>
-      <c r="AJ44" s="24"/>
-      <c r="AK44" s="24"/>
-      <c r="AL44" s="25"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="41">
+        <v>3.5999999999999995E-3</v>
+      </c>
+      <c r="K44" s="41">
+        <v>3.5999999999999995E-3</v>
+      </c>
+      <c r="L44" s="41">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="M44" s="41">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="N44" s="41">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="O44" s="41">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="P44" s="41">
+        <v>6.3015999999999989E-2</v>
+      </c>
+      <c r="Q44" s="41">
+        <v>0.12043199999999998</v>
+      </c>
+      <c r="R44" s="41">
+        <v>0.17784800000000001</v>
+      </c>
+      <c r="S44" s="41">
+        <v>0.37606319999999999</v>
+      </c>
+      <c r="T44" s="41">
+        <v>0.57427839999999997</v>
+      </c>
+      <c r="U44" s="41">
+        <v>0.7724936</v>
+      </c>
+      <c r="V44" s="41">
+        <v>0.97070879999999993</v>
+      </c>
+      <c r="W44" s="41">
+        <v>1.1689240000000001</v>
+      </c>
+      <c r="X44" s="41">
+        <v>1.3671392</v>
+      </c>
+      <c r="Y44" s="41">
+        <v>1.5653543999999999</v>
+      </c>
+      <c r="Z44" s="41">
+        <v>1.7635695999999998</v>
+      </c>
+      <c r="AA44" s="41">
+        <v>1.9617848</v>
+      </c>
+      <c r="AB44" s="41">
+        <v>2.16</v>
+      </c>
+      <c r="AC44" s="23"/>
+      <c r="AD44" s="23"/>
+      <c r="AE44" s="23"/>
+      <c r="AF44" s="23"/>
+      <c r="AG44" s="23"/>
+      <c r="AH44" s="23"/>
+      <c r="AI44" s="23"/>
+      <c r="AJ44" s="23"/>
+      <c r="AK44" s="23"/>
+      <c r="AL44" s="24"/>
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
@@ -5355,7 +5787,7 @@
         <v>17</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L49" s="14" t="s">
         <v>19</v>
@@ -5476,64 +5908,79 @@
       <c r="N50" s="8">
         <v>5</v>
       </c>
-      <c r="P50" s="16">
-        <f>G41/1000</f>
-        <v>4.9889999999999999</v>
-      </c>
-      <c r="Q50" s="16">
-        <f t="shared" ref="Q50:AR51" si="10">H41/1000</f>
-        <v>8.2639999999999993</v>
-      </c>
-      <c r="R50" s="16">
-        <f t="shared" si="10"/>
-        <v>12.603</v>
-      </c>
-      <c r="S50" s="16">
-        <f t="shared" si="10"/>
-        <v>21.079000000000001</v>
-      </c>
-      <c r="T50" s="16">
-        <f t="shared" si="10"/>
-        <v>38.679000000000002</v>
-      </c>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16"/>
+      <c r="T50" s="16"/>
       <c r="U50" s="16">
-        <f t="shared" si="10"/>
-        <v>60.496000000000002</v>
+        <f>L41/1000</f>
+        <v>30.29</v>
       </c>
       <c r="V50" s="16">
-        <f t="shared" si="10"/>
-        <v>86.727999999999994</v>
+        <f>M41/1000+U50</f>
+        <v>41.097999999999999</v>
       </c>
       <c r="W50" s="16">
-        <f t="shared" si="10"/>
-        <v>114.601</v>
+        <f>N41/1000+$V$50</f>
+        <v>66.122600000000006</v>
       </c>
       <c r="X50" s="16">
-        <f t="shared" si="10"/>
-        <v>146.309</v>
+        <f t="shared" ref="X50:AK50" si="10">O41/1000+$V$50</f>
+        <v>80.339200000000005</v>
       </c>
       <c r="Y50" s="16">
         <f t="shared" si="10"/>
-        <v>181.84899999999999</v>
+        <v>94.555800000000005</v>
       </c>
       <c r="Z50" s="16">
         <f t="shared" si="10"/>
-        <v>221.22399999999999</v>
+        <v>108.77239999999999</v>
       </c>
       <c r="AA50" s="16">
         <f t="shared" si="10"/>
-        <v>264.43200000000002</v>
-      </c>
-      <c r="AB50" s="16"/>
-      <c r="AC50" s="16"/>
-      <c r="AD50" s="16"/>
-      <c r="AE50" s="16"/>
-      <c r="AF50" s="16"/>
-      <c r="AG50" s="16"/>
-      <c r="AH50" s="16"/>
-      <c r="AI50" s="16"/>
-      <c r="AJ50" s="16"/>
-      <c r="AK50" s="16"/>
+        <v>122.989</v>
+      </c>
+      <c r="AB50" s="16">
+        <f t="shared" si="10"/>
+        <v>141.75580000000002</v>
+      </c>
+      <c r="AC50" s="16">
+        <f t="shared" si="10"/>
+        <v>160.52260000000001</v>
+      </c>
+      <c r="AD50" s="16">
+        <f t="shared" si="10"/>
+        <v>179.2894</v>
+      </c>
+      <c r="AE50" s="16">
+        <f t="shared" si="10"/>
+        <v>198.05619999999999</v>
+      </c>
+      <c r="AF50" s="16">
+        <f t="shared" si="10"/>
+        <v>216.82299999999998</v>
+      </c>
+      <c r="AG50" s="16">
+        <f t="shared" si="10"/>
+        <v>235.58979999999997</v>
+      </c>
+      <c r="AH50" s="16">
+        <f t="shared" si="10"/>
+        <v>254.35659999999996</v>
+      </c>
+      <c r="AI50" s="16">
+        <f t="shared" si="10"/>
+        <v>273.12339999999995</v>
+      </c>
+      <c r="AJ50" s="16">
+        <f t="shared" si="10"/>
+        <v>291.89019999999994</v>
+      </c>
+      <c r="AK50" s="16">
+        <f t="shared" si="10"/>
+        <v>310.65700000000004</v>
+      </c>
       <c r="AL50" s="16"/>
       <c r="AM50" s="16"/>
       <c r="AN50" s="16"/>
@@ -5561,64 +6008,79 @@
       <c r="N51" s="8">
         <v>5</v>
       </c>
-      <c r="P51" s="16">
-        <f t="shared" ref="P51" si="11">G42/1000</f>
-        <v>1.3580000000000001</v>
-      </c>
-      <c r="Q51" s="16">
-        <f t="shared" si="10"/>
-        <v>2.8130000000000002</v>
-      </c>
-      <c r="R51" s="16">
-        <f t="shared" si="10"/>
-        <v>4.7839999999999998</v>
-      </c>
-      <c r="S51" s="16">
-        <f t="shared" si="10"/>
-        <v>7.056</v>
-      </c>
-      <c r="T51" s="16">
-        <f t="shared" si="10"/>
-        <v>10.823</v>
-      </c>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
       <c r="U51" s="16">
-        <f t="shared" si="10"/>
-        <v>14.423</v>
+        <f>L42/1000</f>
+        <v>22.594000000000001</v>
       </c>
       <c r="V51" s="16">
-        <f t="shared" si="10"/>
-        <v>18.77</v>
+        <f>M42/1000</f>
+        <v>31.445340470809999</v>
       </c>
       <c r="W51" s="16">
-        <f t="shared" si="10"/>
-        <v>43.616</v>
+        <f t="shared" ref="W50:AA51" si="11">N42/1000</f>
+        <v>53.015009948920998</v>
       </c>
       <c r="X51" s="16">
-        <f t="shared" si="10"/>
-        <v>68.462000000000003</v>
+        <f t="shared" si="11"/>
+        <v>74.768033133266016</v>
       </c>
       <c r="Y51" s="16">
-        <f t="shared" si="10"/>
-        <v>93.308000000000007</v>
+        <f t="shared" si="11"/>
+        <v>97.085801374526014</v>
       </c>
       <c r="Z51" s="16">
-        <f t="shared" si="10"/>
-        <v>118.154</v>
+        <f t="shared" si="11"/>
+        <v>119.719602917269</v>
       </c>
       <c r="AA51" s="16">
-        <f t="shared" si="10"/>
-        <v>143</v>
-      </c>
-      <c r="AB51" s="16"/>
-      <c r="AC51" s="16"/>
-      <c r="AD51" s="16"/>
-      <c r="AE51" s="16"/>
-      <c r="AF51" s="16"/>
-      <c r="AG51" s="16"/>
-      <c r="AH51" s="16"/>
-      <c r="AI51" s="16"/>
-      <c r="AJ51" s="16"/>
-      <c r="AK51" s="16"/>
+        <f t="shared" si="11"/>
+        <v>142.35036580480903</v>
+      </c>
+      <c r="AB51" s="16">
+        <f t="shared" ref="AB50:AB51" si="12">S42/1000</f>
+        <v>165.08194181390601</v>
+      </c>
+      <c r="AC51" s="16">
+        <f t="shared" ref="AC50:AC51" si="13">T42/1000</f>
+        <v>187.34688963736804</v>
+      </c>
+      <c r="AD51" s="16">
+        <f t="shared" ref="AD50:AD51" si="14">U42/1000</f>
+        <v>210.02948462770402</v>
+      </c>
+      <c r="AE51" s="16">
+        <f t="shared" ref="AE50:AE51" si="15">V42/1000</f>
+        <v>232.67582927241099</v>
+      </c>
+      <c r="AF51" s="16">
+        <f t="shared" ref="AF50:AF51" si="16">W42/1000</f>
+        <v>254.83899066632299</v>
+      </c>
+      <c r="AG51" s="16">
+        <f t="shared" ref="AG50:AG51" si="17">X42/1000</f>
+        <v>277.00517211469702</v>
+      </c>
+      <c r="AH51" s="16">
+        <f t="shared" ref="AH50:AH51" si="18">Y42/1000</f>
+        <v>299.16226804125699</v>
+      </c>
+      <c r="AI51" s="16">
+        <f t="shared" ref="AI50:AI51" si="19">Z42/1000</f>
+        <v>321.71928957132104</v>
+      </c>
+      <c r="AJ51" s="16">
+        <f t="shared" ref="AJ50:AJ51" si="20">AA42/1000</f>
+        <v>338.75885337760701</v>
+      </c>
+      <c r="AK51" s="16">
+        <f t="shared" ref="AK50:AK51" si="21">AB42/1000</f>
+        <v>407.14097063220697</v>
+      </c>
       <c r="AL51" s="16"/>
       <c r="AM51" s="16"/>
       <c r="AN51" s="16"/>
@@ -5631,77 +6093,95 @@
       <c r="B52" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D52" t="str">
-        <f>D23</f>
-        <v>R-SW_Apt_HET_N1, R-SW_Apt_HET_N2, R-SW_Att_HET_N1, R-SW_Att_HET_N2, R-SW_Det_HET_N1, R-SW_Det_HET_N2</v>
+      <c r="D52" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="G52" s="45" t="s">
+        <v>216</v>
       </c>
       <c r="J52" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K52" s="8">
+      <c r="K52" s="8"/>
+      <c r="L52">
         <v>1</v>
       </c>
       <c r="N52" s="8">
         <v>5</v>
       </c>
-      <c r="P52" s="16">
-        <f>G43*3.6</f>
-        <v>0</v>
-      </c>
-      <c r="Q52" s="16">
-        <f t="shared" ref="Q52:AR52" si="12">H43*3.6</f>
-        <v>0</v>
-      </c>
-      <c r="R52" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="T52" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="P52" s="16"/>
+      <c r="Q52" s="16"/>
+      <c r="R52" s="16"/>
+      <c r="S52" s="16"/>
+      <c r="T52" s="16"/>
       <c r="U52" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>L43*3.6</f>
+        <v>5.0400000000000011E-3</v>
       </c>
       <c r="V52" s="16">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" ref="V52:Z52" si="22">M43*3.6</f>
+        <v>5.0400000000000011E-3</v>
       </c>
       <c r="W52" s="16">
-        <f t="shared" si="12"/>
-        <v>4.6800000000000001E-2</v>
+        <f t="shared" si="22"/>
+        <v>5.0400000000000011E-3</v>
       </c>
       <c r="X52" s="16">
-        <f t="shared" si="12"/>
-        <v>9.3600000000000003E-2</v>
+        <f t="shared" si="22"/>
+        <v>5.0400000000000011E-3</v>
       </c>
       <c r="Y52" s="16">
-        <f t="shared" si="12"/>
-        <v>0.1368</v>
+        <f t="shared" si="22"/>
+        <v>5.6714400000000005E-2</v>
       </c>
       <c r="Z52" s="16">
-        <f t="shared" si="12"/>
-        <v>0.18359999999999999</v>
+        <f t="shared" si="22"/>
+        <v>0.10838879999999999</v>
       </c>
       <c r="AA52" s="16">
-        <f t="shared" si="12"/>
-        <v>0.23040000000000002</v>
-      </c>
-      <c r="AB52" s="16"/>
-      <c r="AC52" s="16"/>
-      <c r="AD52" s="16"/>
-      <c r="AE52" s="16"/>
-      <c r="AF52" s="16"/>
-      <c r="AG52" s="16"/>
-      <c r="AH52" s="16"/>
-      <c r="AI52" s="16"/>
-      <c r="AJ52" s="16"/>
-      <c r="AK52" s="16"/>
+        <f>R43*3.6</f>
+        <v>0.16006320000000002</v>
+      </c>
+      <c r="AB52" s="16">
+        <f t="shared" ref="AB52:AK52" si="23">S43*3.6</f>
+        <v>0.33845688000000007</v>
+      </c>
+      <c r="AC52" s="16">
+        <f t="shared" si="23"/>
+        <v>0.51685056000000007</v>
+      </c>
+      <c r="AD52" s="16">
+        <f t="shared" si="23"/>
+        <v>0.69524424000000007</v>
+      </c>
+      <c r="AE52" s="16">
+        <f t="shared" si="23"/>
+        <v>0.87363792000000007</v>
+      </c>
+      <c r="AF52" s="16">
+        <f t="shared" si="23"/>
+        <v>1.0520316000000001</v>
+      </c>
+      <c r="AG52" s="16">
+        <f t="shared" si="23"/>
+        <v>1.23042528</v>
+      </c>
+      <c r="AH52" s="16">
+        <f t="shared" si="23"/>
+        <v>1.4088189600000001</v>
+      </c>
+      <c r="AI52" s="16">
+        <f t="shared" si="23"/>
+        <v>1.5872126400000002</v>
+      </c>
+      <c r="AJ52" s="16">
+        <f t="shared" si="23"/>
+        <v>1.7656063200000001</v>
+      </c>
+      <c r="AK52" s="16">
+        <f t="shared" si="23"/>
+        <v>1.9440000000000002</v>
+      </c>
       <c r="AL52" s="16"/>
       <c r="AM52" s="16"/>
       <c r="AN52" s="16"/>
@@ -5822,7 +6302,7 @@
       <c r="N56" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <phoneticPr fontId="30" type="noConversion"/>
   <conditionalFormatting sqref="D3:AI9">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0.001</formula>
